--- a/artfynd/A 3521-2025 artfynd.xlsx
+++ b/artfynd/A 3521-2025 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128466809</v>
+        <v>128465650</v>
       </c>
       <c r="B6" t="n">
-        <v>91310</v>
+        <v>79032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,34 +1094,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Simaforsen, Simaforsen, Jmt</t>
+          <t>Husådalen, Husådalen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>401630</v>
+        <v>402436</v>
       </c>
       <c r="R6" t="n">
-        <v>7041636</v>
+        <v>7041567</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128465650</v>
+        <v>128466121</v>
       </c>
       <c r="B7" t="n">
-        <v>79032</v>
+        <v>91378</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>402436</v>
+        <v>402047</v>
       </c>
       <c r="R7" t="n">
-        <v>7041567</v>
+        <v>7041381</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128466121</v>
+        <v>128466809</v>
       </c>
       <c r="B8" t="n">
-        <v>91378</v>
+        <v>91310</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,34 +1298,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>112</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Husådalen, Husådalen, Jmt</t>
+          <t>Simaforsen, Simaforsen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>402047</v>
+        <v>401630</v>
       </c>
       <c r="R8" t="n">
-        <v>7041381</v>
+        <v>7041636</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 3521-2025 artfynd.xlsx
+++ b/artfynd/A 3521-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128464864</v>
       </c>
       <c r="B2" t="n">
-        <v>90131</v>
+        <v>90223</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128465311</v>
       </c>
       <c r="B3" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128464424</v>
       </c>
       <c r="B4" t="n">
-        <v>92057</v>
+        <v>92149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128465176</v>
       </c>
       <c r="B5" t="n">
-        <v>88617</v>
+        <v>88709</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128465650</v>
       </c>
       <c r="B6" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128466121</v>
       </c>
       <c r="B7" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128466809</v>
       </c>
       <c r="B8" t="n">
-        <v>91310</v>
+        <v>91402</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>128464550</v>
       </c>
       <c r="B9" t="n">
-        <v>75156</v>
+        <v>75171</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128464240</v>
       </c>
       <c r="B10" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>128464412</v>
       </c>
       <c r="B11" t="n">
-        <v>78015</v>
+        <v>78060</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 3521-2025 artfynd.xlsx
+++ b/artfynd/A 3521-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128464864</v>
       </c>
       <c r="B2" t="n">
-        <v>90223</v>
+        <v>90229</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128465311</v>
       </c>
       <c r="B3" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128464424</v>
       </c>
       <c r="B4" t="n">
-        <v>92149</v>
+        <v>92155</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128465176</v>
       </c>
       <c r="B5" t="n">
-        <v>88709</v>
+        <v>88715</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128465650</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128466121</v>
       </c>
       <c r="B7" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128466809</v>
       </c>
       <c r="B8" t="n">
-        <v>91402</v>
+        <v>91408</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>128464550</v>
       </c>
       <c r="B9" t="n">
-        <v>75171</v>
+        <v>75175</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128464240</v>
       </c>
       <c r="B10" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>128464412</v>
       </c>
       <c r="B11" t="n">
-        <v>78060</v>
+        <v>78064</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 3521-2025 artfynd.xlsx
+++ b/artfynd/A 3521-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128464864</v>
       </c>
       <c r="B2" t="n">
-        <v>90229</v>
+        <v>90235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128465311</v>
       </c>
       <c r="B3" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128464424</v>
       </c>
       <c r="B4" t="n">
-        <v>92155</v>
+        <v>92161</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128465176</v>
       </c>
       <c r="B5" t="n">
-        <v>88715</v>
+        <v>88721</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128466121</v>
       </c>
       <c r="B7" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128466809</v>
       </c>
       <c r="B8" t="n">
-        <v>91408</v>
+        <v>91414</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128464240</v>
       </c>
       <c r="B10" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 3521-2025 artfynd.xlsx
+++ b/artfynd/A 3521-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128464864</v>
       </c>
       <c r="B2" t="n">
-        <v>90235</v>
+        <v>90237</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128465311</v>
       </c>
       <c r="B3" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128464424</v>
       </c>
       <c r="B4" t="n">
-        <v>92161</v>
+        <v>92163</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128465176</v>
       </c>
       <c r="B5" t="n">
-        <v>88721</v>
+        <v>88723</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128465650</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128466121</v>
       </c>
       <c r="B7" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128466809</v>
       </c>
       <c r="B8" t="n">
-        <v>91414</v>
+        <v>91416</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>128464550</v>
       </c>
       <c r="B9" t="n">
-        <v>75175</v>
+        <v>75177</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128464240</v>
       </c>
       <c r="B10" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>128464412</v>
       </c>
       <c r="B11" t="n">
-        <v>78064</v>
+        <v>78066</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 3521-2025 artfynd.xlsx
+++ b/artfynd/A 3521-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128465311</v>
       </c>
       <c r="B3" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128464424</v>
       </c>
       <c r="B4" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128466121</v>
       </c>
       <c r="B7" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128466809</v>
       </c>
       <c r="B8" t="n">
-        <v>91416</v>
+        <v>91417</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128464240</v>
       </c>
       <c r="B10" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 3521-2025 artfynd.xlsx
+++ b/artfynd/A 3521-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128464864</v>
       </c>
       <c r="B2" t="n">
-        <v>90237</v>
+        <v>90264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128465311</v>
       </c>
       <c r="B3" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128464424</v>
       </c>
       <c r="B4" t="n">
-        <v>92164</v>
+        <v>92191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128465176</v>
       </c>
       <c r="B5" t="n">
-        <v>88723</v>
+        <v>88750</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128465650</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128466121</v>
       </c>
       <c r="B7" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128466809</v>
       </c>
       <c r="B8" t="n">
-        <v>91417</v>
+        <v>91444</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>128464550</v>
       </c>
       <c r="B9" t="n">
-        <v>75177</v>
+        <v>75204</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128464240</v>
       </c>
       <c r="B10" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>128464412</v>
       </c>
       <c r="B11" t="n">
-        <v>78066</v>
+        <v>78093</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 3521-2025 artfynd.xlsx
+++ b/artfynd/A 3521-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128464864</v>
       </c>
       <c r="B2" t="n">
-        <v>90264</v>
+        <v>90269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128465311</v>
       </c>
       <c r="B3" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128464424</v>
       </c>
       <c r="B4" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128465176</v>
       </c>
       <c r="B5" t="n">
-        <v>88750</v>
+        <v>88754</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128465650</v>
       </c>
       <c r="B6" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128466121</v>
       </c>
       <c r="B7" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128466809</v>
       </c>
       <c r="B8" t="n">
-        <v>91444</v>
+        <v>91449</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>128464550</v>
       </c>
       <c r="B9" t="n">
-        <v>75204</v>
+        <v>75205</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128464240</v>
       </c>
       <c r="B10" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>128464412</v>
       </c>
       <c r="B11" t="n">
-        <v>78093</v>
+        <v>78097</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 3521-2025 artfynd.xlsx
+++ b/artfynd/A 3521-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128464864</v>
       </c>
       <c r="B2" t="n">
-        <v>90269</v>
+        <v>90274</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128465311</v>
       </c>
       <c r="B3" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128464424</v>
       </c>
       <c r="B4" t="n">
-        <v>92196</v>
+        <v>92201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128465176</v>
       </c>
       <c r="B5" t="n">
-        <v>88754</v>
+        <v>88755</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128466121</v>
       </c>
       <c r="B7" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128466809</v>
       </c>
       <c r="B8" t="n">
-        <v>91449</v>
+        <v>91454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128464240</v>
       </c>
       <c r="B10" t="n">
-        <v>92434</v>
+        <v>92439</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 3521-2025 artfynd.xlsx
+++ b/artfynd/A 3521-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128464864</v>
       </c>
       <c r="B2" t="n">
-        <v>90274</v>
+        <v>90278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128465311</v>
       </c>
       <c r="B3" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128464424</v>
       </c>
       <c r="B4" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128465176</v>
       </c>
       <c r="B5" t="n">
-        <v>88755</v>
+        <v>88759</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128465650</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128466121</v>
       </c>
       <c r="B7" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128466809</v>
       </c>
       <c r="B8" t="n">
-        <v>91454</v>
+        <v>91458</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>128464550</v>
       </c>
       <c r="B9" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128464240</v>
       </c>
       <c r="B10" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>128464412</v>
       </c>
       <c r="B11" t="n">
-        <v>78097</v>
+        <v>78101</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 3521-2025 artfynd.xlsx
+++ b/artfynd/A 3521-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128464864</v>
       </c>
       <c r="B2" t="n">
-        <v>90278</v>
+        <v>90283</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128465311</v>
       </c>
       <c r="B3" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128464424</v>
       </c>
       <c r="B4" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128465176</v>
       </c>
       <c r="B5" t="n">
-        <v>88759</v>
+        <v>88764</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128465650</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128466121</v>
       </c>
       <c r="B7" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128466809</v>
       </c>
       <c r="B8" t="n">
-        <v>91458</v>
+        <v>91463</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>128464550</v>
       </c>
       <c r="B9" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128464240</v>
       </c>
       <c r="B10" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>128464412</v>
       </c>
       <c r="B11" t="n">
-        <v>78101</v>
+        <v>78042</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
